--- a/assets/constructions/examples/ctd_me4.xlsx
+++ b/assets/constructions/examples/ctd_me4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,34 +619,69 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2223-3522 Р6М5 ГОСТ 23248-78</t>
+          <t>2223-0124 Р6М5 ГОСТ 17026-71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ПЕТРОФОРТ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>ТИЗ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2223-0124</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SH</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>PKN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11</v>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -656,7 +691,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MKG_H:2</t>
+          <t>MKG_H:1</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -678,28 +713,28 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ГОСТ 23248-78</t>
+          <t>ГОСТ 17026-71</t>
         </is>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
@@ -711,7 +746,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ГОСТ 23248-78</t>
+          <t>ГОСТ 17026-71</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -723,36 +758,53 @@
         <v>1</v>
       </c>
       <c r="AL2" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>PMKN</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2223-2462 Р6М5 ГОСТ 23248-78</t>
+          <t>2223-0112 Р18 ГОСТ 17026-71 с покрытием</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ПЕТРОФОРТ</t>
+          <t>ФРЕЗЕР</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SH</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PKN</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
+        <v>10</v>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -762,7 +814,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MKG_H:2</t>
+          <t>MKG_H:1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -773,18 +825,18 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Р6М5</t>
+          <t>Р18</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>TiN</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ГОСТ 23248-78</t>
+          <t>ГОСТ 17026-71 с покрытием</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -794,18 +846,18 @@
         <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
@@ -817,7 +869,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>ГОСТ 23248-78</t>
+          <t>ГОСТ 17026-71 с покрытием</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -829,42 +881,61 @@
         <v>1</v>
       </c>
       <c r="AL3" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2223-0117 Р18 ГОСТ 17026-71 с покрытием</t>
+          <t>1Ф/3374-36-120-245-4-Z4 Р18 1617</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ФРЕЗЕР</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>ТИЗ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1Ф/3374</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PKNS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PKN</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>90</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
       <c r="K4" t="n">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -874,7 +945,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MKG_H:1</t>
+          <t>MKG_H:4</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -891,34 +962,34 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>TiN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ГОСТ 17026-71 с покрытием</t>
+          <t>Нормаль завода</t>
         </is>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>245</v>
+      </c>
       <c r="Z4" t="n">
-        <v>92</v>
+        <v>245</v>
       </c>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>45</v>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
@@ -929,7 +1000,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>ГОСТ 17026-71 с покрытием</t>
+          <t>2019/Каталог инструмента ОПН</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -938,16 +1009,27 @@
         </is>
       </c>
       <c r="AK4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2223-0286 11РЗАМЗФ2 ГОСТ 17026-71</t>
+          <t>1Ф/3374-26-90-190-3-Z5 Р6М5К5 1617</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -957,26 +1039,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2223-0286</t>
+          <t>1Ф/3374</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PKN</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>PMKN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>90</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -986,7 +1076,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MKG_H:5</t>
+          <t>MKG_H:3</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -997,7 +1087,7 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>11РЗАМЗФ2</t>
+          <t>Р6М5К5</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -1008,29 +1098,29 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ГОСТ 17026-71</t>
+          <t>Нормаль завода</t>
         </is>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X5" t="n">
-        <v>75</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>190</v>
+      </c>
       <c r="Z5" t="n">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>45</v>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
@@ -1041,7 +1131,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>ГОСТ 17026-71</t>
+          <t>2019/Каталог инструмента ОПН</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1050,48 +1140,53 @@
         </is>
       </c>
       <c r="AK5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="b">
         <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2223-0896 Р18 ГОСТ 17026-71 с покрытием</t>
+          <t>2223-4075 Р6М5 ГОСТ 23248-78</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ФРЕЗЕР</t>
+          <t>ПЕТРОФОРТ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PKN</t>
-        </is>
-      </c>
+          <t>SH</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>50</v>
-      </c>
-      <c r="G6" t="n">
-        <v>50</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="L6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="b">
         <v>1</v>
@@ -1109,39 +1204,39 @@
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Р18</t>
+          <t>Р6М5</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>TiN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ГОСТ 17026-71 с покрытием</t>
+          <t>ГОСТ 23248-78</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
         <v>4</v>
       </c>
       <c r="X6" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
@@ -1153,7 +1248,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>ГОСТ 17026-71 с покрытием</t>
+          <t>ГОСТ 23248-78</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1165,7 +1260,18 @@
         <v>1</v>
       </c>
       <c r="AL6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>SH</t>
+        </is>
       </c>
     </row>
   </sheetData>
